--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N165_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N165_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.63461363329992</v>
+        <v>6.928124715411237</v>
       </c>
       <c r="D2" t="n">
-        <v>42.85999776850969</v>
+        <v>6.964749637382825</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28250436505721</v>
+        <v>1.833406959321796</v>
       </c>
       <c r="F2" t="n">
-        <v>11.49087106521223</v>
+        <v>1.867266548096986</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.21788658877483</v>
+        <v>3.44790657067591</v>
       </c>
       <c r="D3" t="n">
-        <v>20.92761042594062</v>
+        <v>3.40073669421535</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28250436505721</v>
+        <v>1.833406959321796</v>
       </c>
       <c r="F3" t="n">
-        <v>11.49087106521223</v>
+        <v>1.867266548096986</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.42341728955993</v>
+        <v>2.993805309553488</v>
       </c>
       <c r="D4" t="n">
-        <v>17.97058832500939</v>
+        <v>2.920220602814025</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28250436505721</v>
+        <v>1.833406959321796</v>
       </c>
       <c r="F4" t="n">
-        <v>11.49087106521223</v>
+        <v>1.867266548096986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.95300463198659</v>
+        <v>6.817363252697822</v>
       </c>
       <c r="D5" t="n">
-        <v>41.78583794127827</v>
+        <v>6.790198665457719</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28250436505721</v>
+        <v>1.833406959321796</v>
       </c>
       <c r="F5" t="n">
-        <v>11.49087106521223</v>
+        <v>1.867266548096986</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
